--- a/Reports/Debt/Report1/pattern.xlsx
+++ b/Reports/Debt/Report1/pattern.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\Debt\Report1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03524749-AC7A-4442-A2ED-E44CA2E9FA0C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110"/>
+    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$2:$J$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -153,12 +159,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -310,26 +316,34 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="2"/>
-    <cellStyle name="Обычный 5" xfId="3"/>
-    <cellStyle name="Обычный 6" xfId="4"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -376,7 +390,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -408,9 +422,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -442,6 +474,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -617,12 +667,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W7"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.42578125" style="1" customWidth="1"/>
@@ -636,7 +686,7 @@
     <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="L1" s="15"/>
       <c r="M1" s="2" t="s">
         <v>3</v>
@@ -654,19 +704,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
       <c r="K2" s="20"/>
       <c r="L2" s="16"/>
       <c r="M2" s="2"/>
@@ -675,23 +725,23 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:23">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
       <c r="K3" s="20"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:23" ht="36">
+    <row r="4" spans="1:23" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>15</v>
       </c>
@@ -733,7 +783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>25</v>
       </c>
@@ -781,7 +831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="18" customHeight="1">
+    <row r="6" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="24" t="s">
         <v>13</v>
       </c>
@@ -790,16 +840,16 @@
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="26" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="25"/>
@@ -826,7 +876,7 @@
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
     </row>
-    <row r="7" spans="1:23" ht="18" customHeight="1">
+    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>42</v>
       </c>
@@ -835,16 +885,16 @@
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="27" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="13"/>
@@ -885,15 +935,15 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="69" fitToHeight="50" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="75" fitToHeight="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -902,9 +952,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
